--- a/KNN練習題/114學年度上學期資料探勘_期中考考試練習.xlsx
+++ b/KNN練習題/114學年度上學期資料探勘_期中考考試練習.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\1.教學\3.資料探勘DataMining\期中考期末考\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\1.教學\3.資料探勘DataMining\Data Mining MarkDown\KNN練習題\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -208,8 +208,20 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>題目2：請說明什麼是</t>
+    <t>113學年度上學期資料探勘期中考試(練習題)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>題目2說明:(35分)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>題目1說明:(35分)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>題目5：請說明什麼為什麼在資料探勘前，資料必須作</t>
     </r>
     <r>
       <rPr>
@@ -219,7 +231,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t>均值K-means分群分析</t>
+      <t>「資料標準化」</t>
     </r>
     <r>
       <rPr>
@@ -229,8 +241,40 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t>，須說明均值K-means的原理?   (6分)</t>
-    </r>
+      <t>呢?（也可使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3333FF"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>「資料正規化」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>) (6分)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>標準化</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.因兩個欄位的尺度不相同，因此資料須先作資料正規化後方能計算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.因兩個欄位的尺度不相同，因此資料須先作資料正規化後方能計算</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -261,6 +305,32 @@
   </si>
   <si>
     <r>
+      <t>題目2：請說明什麼是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3333FF"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">均值K-means分群分析 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>? 須說明均值K-means的計算原理(演算法Algorithm)   (6分)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t>題目4：請說明什麼是</t>
     </r>
     <r>
@@ -281,78 +351,8 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t>(Ｋ-Nearest-Neighbor,KNN)，須說明最近鄰居法分類法的原理 (6分)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>113學年度上學期資料探勘期中考試(練習題)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>題目2說明:(35分)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>題目1說明:(35分)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>題目5：請說明什麼為什麼在資料探勘前，資料必須作</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3333FF"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>「資料標準化」</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>呢?（也可使用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3333FF"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>「資料正規化」</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>) (6分)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>標準化</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.因兩個欄位的尺度不相同，因此資料須先作資料正規化後方能計算</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5.因兩個欄位的尺度不相同，因此資料須先作資料正規化後方能計算</t>
+      <t>(Ｋ-Nearest-Neighbor,KNN) ?須說明最近鄰居法分類法的計算原理(演算法Algorithm)  (6分)</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1018,7 +1018,7 @@
   <sheetData>
     <row r="1" spans="1:22" s="1" customFormat="1">
       <c r="A1" s="25" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -1070,7 +1070,7 @@
     </row>
     <row r="3" spans="1:22" s="1" customFormat="1">
       <c r="A3" s="21" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -1174,7 +1174,7 @@
     </row>
     <row r="7" spans="1:22" s="1" customFormat="1">
       <c r="A7" s="21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B7" s="22"/>
       <c r="C7" s="22"/>
@@ -1271,7 +1271,7 @@
         <v>19</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G13" s="20"/>
     </row>
@@ -1458,7 +1458,7 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="29" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -1538,7 +1538,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="29" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="30"/>
@@ -1575,7 +1575,7 @@
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
       <c r="H9" s="20" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I9" s="20"/>
     </row>
@@ -1900,22 +1900,22 @@
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="9" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="9" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="9" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/KNN練習題/114學年度上學期資料探勘_期中考考試練習.xlsx
+++ b/KNN練習題/114學年度上學期資料探勘_期中考考試練習.xlsx
@@ -346,12 +346,22 @@
     <r>
       <rPr>
         <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>(Ｋ-Nearest-Neighbor,KNN) ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="標楷體"/>
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t>(Ｋ-Nearest-Neighbor,KNN) ?須說明最近鄰居法分類法的計算原理(演算法Algorithm)  (6分)</t>
+      <t xml:space="preserve"> 須說明最近鄰居法分類法的計算原理(演算法Algorithm)  (6分)</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -719,10 +729,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF0000FF"/>
       <color rgb="FF3399FF"/>
       <color rgb="FFFF99FF"/>
       <color rgb="FFFF9900"/>
-      <color rgb="FF0000FF"/>
       <color rgb="FFFF0D0D"/>
       <color rgb="FF00CCFF"/>
       <color rgb="FFFF66FF"/>
@@ -1921,5 +1931,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>